--- a/data/trans_camb/P1409-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1409-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,32</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,26</t>
+          <t>-1,3; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,02</t>
+          <t>-0,08; 3,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,39</t>
+          <t>-1,24; 3,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,96</t>
+          <t>0,46; 4,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,18</t>
+          <t>-0,66; 2,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,79</t>
+          <t>0,73; 3,71</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>120,41%</t>
+          <t>113,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175,68%</t>
+          <t>179,84%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147,75%</t>
+          <t>146,39%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,31; 286,33</t>
+          <t>-63,67; 276,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 636,93</t>
+          <t>-17,69; 423,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,68; 595,64</t>
+          <t>-56,6; 661,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 988,4</t>
+          <t>-1,82; 965,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 243,88</t>
+          <t>-34,78; 239,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,63; 418,58</t>
+          <t>20,39; 421,33</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,19</t>
+          <t>-1,07; 3,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,5</t>
+          <t>0,42; 5,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,75</t>
+          <t>-2,75; 3,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,96</t>
+          <t>-0,79; 5,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,77</t>
+          <t>-0,95; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,65</t>
+          <t>0,51; 4,43</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>185,53%</t>
+          <t>177,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 531,88</t>
+          <t>-60,92; 577,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 830,92</t>
+          <t>-12,17; 873,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,78; 156,88</t>
+          <t>-50,44; 177,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 199,1</t>
+          <t>-17,44; 208,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 159,42</t>
+          <t>-29,28; 174,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 259,71</t>
+          <t>3,09; 245,17</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>1,13</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,6</t>
+          <t>-1,42; 1,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,94</t>
+          <t>-0,63; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,23</t>
+          <t>-2,88; 4,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,39</t>
+          <t>-2,09; 4,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,48</t>
+          <t>-1,44; 1,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,89</t>
+          <t>-0,41; 2,92</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 153,71</t>
+          <t>-60,41; 189,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,88; 159,4</t>
+          <t>-32,16; 326,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,04; 421,8</t>
+          <t>-79,1; 382,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 338,23</t>
+          <t>-50,08; 294,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 114,17</t>
+          <t>-55,63; 108,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 116,76</t>
+          <t>-19,65; 212,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,28</t>
+          <t>-1,15; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,26</t>
+          <t>0,24; 3,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,13</t>
+          <t>-1,3; 2,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,51</t>
+          <t>-0,03; 3,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,18</t>
+          <t>-0,8; 1,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,49</t>
+          <t>0,77; 2,94</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 92,59</t>
+          <t>-43,13; 83,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 225,45</t>
+          <t>3,88; 227,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 120,86</t>
+          <t>-37,46; 113,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 121,18</t>
+          <t>-2,67; 181,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 60,77</t>
+          <t>-28,06; 73,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 139,44</t>
+          <t>23,38; 154,12</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>2,47</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,17</t>
+          <t>-0,59; 3,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,48</t>
+          <t>0,76; 6,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,44</t>
+          <t>0,16; 4,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 32,64</t>
+          <t>0,34; 3,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,32</t>
+          <t>0,26; 3,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 28,57</t>
+          <t>1,06; 3,95</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>181,05%</t>
+          <t>144,69%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>320,08%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>284,44%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 241,07</t>
+          <t>-22,08; 228,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,67; 533,28</t>
+          <t>7,76; 419,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3,22; 206,37</t>
+          <t>2,74; 208,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30,43; 1359,5</t>
+          <t>7,25; 193,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,21; 164,71</t>
+          <t>5,23; 152,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,04; 1243,7</t>
+          <t>29,5; 195,7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,65</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,46</t>
+          <t>-1,02; 5,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 7,97</t>
+          <t>-2,39; 8,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,06</t>
+          <t>0,01; 3,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,87</t>
+          <t>0,26; 3,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,04</t>
+          <t>0,32; 3,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,98</t>
+          <t>0,32; 3,49</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 465,59</t>
+          <t>-35,16; 418,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-94,06; 547,93</t>
+          <t>-93,97; 642,96</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1,61; 171,44</t>
+          <t>-1,38; 167,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16,52; 209,58</t>
+          <t>7,15; 174,15</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,07; 163,88</t>
+          <t>7,79; 159,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,86; 202,98</t>
+          <t>6,02; 186,0</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,36</t>
+          <t>-0,08; 1,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>1,09; 2,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,15</t>
+          <t>0,36; 2,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,38</t>
+          <t>1,23; 2,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,46</t>
+          <t>0,32; 1,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,39</t>
+          <t>1,38; 2,59</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>102,21%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>132,38%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>116,8%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 85,78</t>
+          <t>-3,62; 91,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>33,14; 176,69</t>
+          <t>49,89; 182,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,81; 93,61</t>
+          <t>10,87; 93,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51,54; 445,47</t>
+          <t>37,72; 118,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,98; 71,85</t>
+          <t>12,21; 70,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,04; 265,69</t>
+          <t>52,98; 125,18</t>
         </is>
       </c>
     </row>
